--- a/registration_forms/033_scriptwriting_residency_application_form--registration_forms.xlsx
+++ b/registration_forms/033_scriptwriting_residency_application_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -811,282 +811,6 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>submit_label</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Review and Submit</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>first_name</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>last_name</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Last Name</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>residency_address</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Residency Address</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>application_type</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Application Type</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>program_name</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Program Name</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>start_date</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Start Date</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>duration</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Duration</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>end_date</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>End Date</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>purpose</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1098,12 +822,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option':_'residency_for_writers'}</t>
+          <t>residency_for_writers</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option': 'Residency for Writers'}</t>
+          <t>Residency for Writers</t>
         </is>
       </c>
     </row>
@@ -1148,46 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option':_'residency_for_artists'}</t>
+          <t>residency_for_artists</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option': 'Residency for Artists'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>application_type_choices</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>{'option':_'residency_for_writers'}</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>{'option': 'Residency for Writers'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>application_type_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>{'option':_'residency_for_artists'}</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>{'option': 'Residency for Artists'}</t>
+          <t>Residency for Artists</t>
         </is>
       </c>
     </row>
